--- a/output/stock_quant_scores/JPM_info.xlsx
+++ b/output/stock_quant_scores/JPM_info.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FQ2"/>
+  <dimension ref="A1:FU2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1061,230 +1061,250 @@
       </c>
       <c r="DX1" s="1" t="inlineStr">
         <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DY1" s="1" t="inlineStr">
+        <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="DY1" s="1" t="inlineStr">
+      <c r="DZ1" s="1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="EA1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketTime</t>
+        </is>
+      </c>
+      <c r="EB1" s="1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="DZ1" s="1" t="inlineStr">
+      <c r="EC1" s="1" t="inlineStr">
         <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="EA1" s="1" t="inlineStr">
+      <c r="ED1" s="1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="EB1" s="1" t="inlineStr">
+      <c r="EE1" s="1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="EC1" s="1" t="inlineStr">
+      <c r="EF1" s="1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="ED1" s="1" t="inlineStr">
+      <c r="EG1" s="1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="EE1" s="1" t="inlineStr">
+      <c r="EH1" s="1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="EF1" s="1" t="inlineStr">
+      <c r="EI1" s="1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
         </is>
       </c>
-      <c r="EG1" s="1" t="inlineStr">
+      <c r="EJ1" s="1" t="inlineStr">
         <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="EH1" s="1" t="inlineStr">
+      <c r="EK1" s="1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
         </is>
       </c>
-      <c r="EI1" s="1" t="inlineStr">
+      <c r="EL1" s="1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="EM1" s="1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EN1" s="1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampStart</t>
+        </is>
+      </c>
+      <c r="EO1" s="1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EP1" s="1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="EQ1" s="1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="ER1" s="1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="ES1" s="1" t="inlineStr">
+        <is>
+          <t>epsCurrentYear</t>
+        </is>
+      </c>
+      <c r="ET1" s="1" t="inlineStr">
+        <is>
+          <t>priceEpsCurrentYear</t>
+        </is>
+      </c>
+      <c r="EU1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EV1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EW1" s="1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EX1" s="1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EY1" s="1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="EZ1" s="1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="FA1" s="1" t="inlineStr">
+        <is>
+          <t>averageAnalystRating</t>
+        </is>
+      </c>
+      <c r="FB1" s="1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="FC1" s="1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="FD1" s="1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="FE1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="FF1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketPrice</t>
+        </is>
+      </c>
+      <c r="FG1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketChange</t>
+        </is>
+      </c>
+      <c r="FH1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="FI1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="FJ1" s="1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="FK1" s="1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="FL1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="FM1" s="1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="EJ1" s="1" t="inlineStr">
+      <c r="FN1" s="1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="EK1" s="1" t="inlineStr">
+      <c r="FO1" s="1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="EL1" s="1" t="inlineStr">
+      <c r="FP1" s="1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="EM1" s="1" t="inlineStr">
+      <c r="FQ1" s="1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="EN1" s="1" t="inlineStr">
+      <c r="FR1" s="1" t="inlineStr">
         <is>
           <t>dividendDate</t>
         </is>
       </c>
-      <c r="EO1" s="1" t="inlineStr">
+      <c r="FS1" s="1" t="inlineStr">
         <is>
           <t>earningsTimestamp</t>
         </is>
       </c>
-      <c r="EP1" s="1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EQ1" s="1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="ER1" s="1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampStart</t>
-        </is>
-      </c>
-      <c r="ES1" s="1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampEnd</t>
-        </is>
-      </c>
-      <c r="ET1" s="1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="EU1" s="1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EV1" s="1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="EW1" s="1" t="inlineStr">
-        <is>
-          <t>epsCurrentYear</t>
-        </is>
-      </c>
-      <c r="EX1" s="1" t="inlineStr">
-        <is>
-          <t>priceEpsCurrentYear</t>
-        </is>
-      </c>
-      <c r="EY1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EZ1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="FA1" s="1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="FB1" s="1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="FC1" s="1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="FD1" s="1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="FE1" s="1" t="inlineStr">
-        <is>
-          <t>averageAnalystRating</t>
-        </is>
-      </c>
-      <c r="FF1" s="1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="FG1" s="1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="FH1" s="1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="FI1" s="1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="FJ1" s="1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="FK1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="FL1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="FM1" s="1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="FN1" s="1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="FO1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="FP1" s="1" t="inlineStr">
+      <c r="FT1" s="1" t="inlineStr">
         <is>
           <t>displayName</t>
         </is>
       </c>
-      <c r="FQ1" s="1" t="inlineStr">
+      <c r="FU1" s="1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -1410,34 +1430,34 @@
         <v>2</v>
       </c>
       <c r="AC2" t="n">
-        <v>312.74</v>
+        <v>313.45</v>
       </c>
       <c r="AD2" t="n">
-        <v>314.05</v>
+        <v>314.9</v>
       </c>
       <c r="AE2" t="n">
-        <v>311.665</v>
+        <v>313.704</v>
       </c>
       <c r="AF2" t="n">
-        <v>316.5773</v>
+        <v>317.81</v>
       </c>
       <c r="AG2" t="n">
-        <v>312.74</v>
+        <v>313.45</v>
       </c>
       <c r="AH2" t="n">
-        <v>314.05</v>
+        <v>314.9</v>
       </c>
       <c r="AI2" t="n">
-        <v>311.665</v>
+        <v>313.704</v>
       </c>
       <c r="AJ2" t="n">
-        <v>316.5773</v>
+        <v>317.81</v>
       </c>
       <c r="AK2" t="n">
         <v>6</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AM2" t="n">
         <v>1759708800</v>
@@ -1452,67 +1472,67 @@
         <v>1.129</v>
       </c>
       <c r="AQ2" t="n">
-        <v>16.048338</v>
+        <v>16.208204</v>
       </c>
       <c r="AR2" t="n">
-        <v>18.703888</v>
+        <v>18.880526</v>
       </c>
       <c r="AS2" t="n">
-        <v>3252573</v>
+        <v>7255792</v>
       </c>
       <c r="AT2" t="n">
-        <v>3252565</v>
+        <v>7255792</v>
       </c>
       <c r="AU2" t="n">
-        <v>8513839</v>
+        <v>8323593</v>
       </c>
       <c r="AV2" t="n">
-        <v>9660450</v>
+        <v>9568010</v>
       </c>
       <c r="AW2" t="n">
-        <v>9660450</v>
+        <v>9568010</v>
       </c>
       <c r="AX2" t="n">
-        <v>313.02</v>
+        <v>316.06</v>
       </c>
       <c r="AY2" t="n">
-        <v>313.08</v>
+        <v>316.54</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="BA2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB2" t="n">
-        <v>860956393472</v>
+        <v>869087182848</v>
       </c>
       <c r="BC2" t="n">
         <v>202.16</v>
       </c>
       <c r="BD2" t="n">
-        <v>316.5773</v>
+        <v>317.81</v>
       </c>
       <c r="BE2" t="n">
-        <v>316.31</v>
+        <v>317.81</v>
       </c>
       <c r="BF2" t="n">
         <v>3.208333</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.257813</v>
+        <v>5.3074675</v>
       </c>
       <c r="BH2" t="n">
-        <v>297.2058</v>
+        <v>298.819</v>
       </c>
       <c r="BI2" t="n">
-        <v>265.74686</v>
+        <v>266.7803</v>
       </c>
       <c r="BJ2" t="n">
         <v>5.3</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.016946986</v>
+        <v>0.016908597</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
@@ -1523,7 +1543,7 @@
         <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>507955019776</v>
+        <v>517084217344</v>
       </c>
       <c r="BO2" t="n">
         <v>0.34524</v>
@@ -1535,31 +1555,31 @@
         <v>2749753854</v>
       </c>
       <c r="BR2" t="n">
-        <v>26460443</v>
+        <v>26956512</v>
       </c>
       <c r="BS2" t="n">
-        <v>22697535</v>
+        <v>24216278</v>
       </c>
       <c r="BT2" t="n">
-        <v>1753920000</v>
+        <v>1755216000</v>
       </c>
       <c r="BU2" t="n">
-        <v>1756425600</v>
+        <v>1757894400</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.009599999499999999</v>
+        <v>0.0098</v>
       </c>
       <c r="BW2" t="n">
         <v>0.00466</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.74483</v>
+        <v>0.7448399999999999</v>
       </c>
       <c r="BY2" t="n">
-        <v>3.54</v>
+        <v>3.8</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.0097</v>
+        <v>0.0098</v>
       </c>
       <c r="CA2" t="n">
         <v>2749753854</v>
@@ -1568,7 +1588,7 @@
         <v>122.512</v>
       </c>
       <c r="CC2" t="n">
-        <v>2.5556931</v>
+        <v>2.579829</v>
       </c>
       <c r="CD2" t="n">
         <v>1735603200</v>
@@ -1586,7 +1606,7 @@
         <v>55154999296</v>
       </c>
       <c r="CI2" t="n">
-        <v>19.51</v>
+        <v>19.5</v>
       </c>
       <c r="CJ2" t="n">
         <v>16.74</v>
@@ -1600,13 +1620,13 @@
         <v>960768000</v>
       </c>
       <c r="CM2" t="n">
-        <v>3.102</v>
+        <v>3.158</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.4878919</v>
+        <v>0.49890924</v>
       </c>
       <c r="CO2" t="n">
-        <v>0.16333759</v>
+        <v>0.1529237</v>
       </c>
       <c r="CP2" t="n">
         <v>1.4</v>
@@ -1620,7 +1640,7 @@
         </is>
       </c>
       <c r="CS2" t="n">
-        <v>313.1031</v>
+        <v>316.06</v>
       </c>
       <c r="CT2" t="n">
         <v>350</v>
@@ -1727,172 +1747,184 @@
       </c>
       <c r="DW2" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="DX2" t="inlineStr">
         <is>
+          <t>JP Morgan Chase &amp; Co.</t>
+        </is>
+      </c>
+      <c r="DY2" t="inlineStr">
+        <is>
           <t>[{'header': 'Dividend', 'message': 'JPM announced a cash dividend of 1.50 with an ex-date of Oct. 6, 2025', 'meta': {'eventType': 'DIVIDEND', 'dateEpochMs': 1759723200000, 'amount': '1.50'}}]</t>
         </is>
       </c>
-      <c r="DY2" t="n">
-        <v>1758740015</v>
-      </c>
       <c r="DZ2" t="inlineStr">
         <is>
+          <t>JPMorgan Chase &amp; Co.</t>
+        </is>
+      </c>
+      <c r="EA2" t="n">
+        <v>1758931187</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>1758916802</v>
+      </c>
+      <c r="EC2" t="inlineStr">
+        <is>
           <t>NYQ</t>
         </is>
       </c>
-      <c r="EA2" t="inlineStr">
+      <c r="ED2" t="inlineStr">
         <is>
           <t>finmb_658776</t>
         </is>
       </c>
-      <c r="EB2" t="inlineStr">
+      <c r="EE2" t="inlineStr">
         <is>
           <t>America/New_York</t>
         </is>
       </c>
-      <c r="EC2" t="inlineStr">
+      <c r="EF2" t="inlineStr">
         <is>
           <t>EDT</t>
         </is>
       </c>
-      <c r="ED2" t="n">
+      <c r="EG2" t="n">
         <v>-14400000</v>
       </c>
-      <c r="EE2" t="inlineStr">
+      <c r="EH2" t="inlineStr">
         <is>
           <t>us_market</t>
         </is>
       </c>
-      <c r="EF2" t="b">
+      <c r="EI2" t="b">
         <v>0</v>
       </c>
-      <c r="EG2" t="n">
-        <v>0.11610224</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>313.1031</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>0.5487885</v>
-      </c>
-      <c r="EJ2" t="inlineStr">
-        <is>
-          <t>202.16 - 316.5773</t>
-        </is>
+      <c r="EJ2" t="n">
+        <v>0.832664</v>
       </c>
       <c r="EK2" t="n">
-        <v>-3.4742126</v>
+        <v>316.06</v>
       </c>
       <c r="EL2" t="n">
-        <v>-0.0109742945</v>
+        <v>1760445000</v>
       </c>
       <c r="EM2" t="n">
-        <v>48.789192</v>
+        <v>1760445000</v>
       </c>
       <c r="EN2" t="n">
-        <v>1761868800</v>
+        <v>1760445000</v>
       </c>
       <c r="EO2" t="n">
         <v>1760445000</v>
       </c>
-      <c r="EP2" t="n">
+      <c r="EP2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EQ2" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="ER2" t="n">
+        <v>16.74</v>
+      </c>
+      <c r="ES2" t="n">
+        <v>19.44051</v>
+      </c>
+      <c r="ET2" t="n">
+        <v>16.257805</v>
+      </c>
+      <c r="EU2" t="n">
+        <v>17.240997</v>
+      </c>
+      <c r="EV2" t="n">
+        <v>0.057697125</v>
+      </c>
+      <c r="EW2" t="n">
+        <v>49.279694</v>
+      </c>
+      <c r="EX2" t="n">
+        <v>0.18472013</v>
+      </c>
+      <c r="EY2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA2" t="inlineStr">
+        <is>
+          <t>2.3 - Buy</t>
+        </is>
+      </c>
+      <c r="FB2" t="b">
+        <v>0</v>
+      </c>
+      <c r="FC2" t="b">
+        <v>1</v>
+      </c>
+      <c r="FD2" t="n">
+        <v>322151400000</v>
+      </c>
+      <c r="FE2" t="n">
+        <v>0.07593186</v>
+      </c>
+      <c r="FF2" t="n">
+        <v>316.3</v>
+      </c>
+      <c r="FG2" t="n">
+        <v>0.23999023</v>
+      </c>
+      <c r="FH2" t="n">
+        <v>2.60999</v>
+      </c>
+      <c r="FI2" t="inlineStr">
+        <is>
+          <t>313.704 - 317.81</t>
+        </is>
+      </c>
+      <c r="FJ2" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="FK2" t="n">
+        <v>8323593</v>
+      </c>
+      <c r="FL2" t="n">
+        <v>113.899994</v>
+      </c>
+      <c r="FM2" t="n">
+        <v>0.56341505</v>
+      </c>
+      <c r="FN2" t="inlineStr">
+        <is>
+          <t>202.16 - 317.81</t>
+        </is>
+      </c>
+      <c r="FO2" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="FP2" t="n">
+        <v>-0.0055064345</v>
+      </c>
+      <c r="FQ2" t="n">
+        <v>49.890923</v>
+      </c>
+      <c r="FR2" t="n">
+        <v>1761868800</v>
+      </c>
+      <c r="FS2" t="n">
         <v>1760445000</v>
       </c>
-      <c r="EQ2" t="n">
-        <v>1760445000</v>
-      </c>
-      <c r="ER2" t="n">
-        <v>1760445000</v>
-      </c>
-      <c r="ES2" t="n">
-        <v>1760445000</v>
-      </c>
-      <c r="ET2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EU2" t="n">
-        <v>19.51</v>
-      </c>
-      <c r="EV2" t="n">
-        <v>16.74</v>
-      </c>
-      <c r="EW2" t="n">
-        <v>19.44051</v>
-      </c>
-      <c r="EX2" t="n">
-        <v>16.105703</v>
-      </c>
-      <c r="EY2" t="n">
-        <v>15.897278</v>
-      </c>
-      <c r="EZ2" t="n">
-        <v>0.053489123</v>
-      </c>
-      <c r="FA2" t="n">
-        <v>47.35623</v>
-      </c>
-      <c r="FB2" t="n">
-        <v>0.17820053</v>
-      </c>
-      <c r="FC2" t="n">
-        <v>15</v>
-      </c>
-      <c r="FD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="FE2" t="inlineStr">
-        <is>
-          <t>2.3 - Buy</t>
-        </is>
-      </c>
-      <c r="FF2" t="b">
-        <v>0</v>
-      </c>
-      <c r="FG2" t="inlineStr">
-        <is>
-          <t>JP Morgan Chase &amp; Co.</t>
-        </is>
-      </c>
-      <c r="FH2" t="inlineStr">
-        <is>
-          <t>JPMorgan Chase &amp; Co.</t>
-        </is>
-      </c>
-      <c r="FI2" t="b">
-        <v>1</v>
-      </c>
-      <c r="FJ2" t="n">
-        <v>322151400000</v>
-      </c>
-      <c r="FK2" t="n">
-        <v>0.36309814</v>
-      </c>
-      <c r="FL2" t="inlineStr">
-        <is>
-          <t>311.665 - 316.5773</t>
-        </is>
-      </c>
-      <c r="FM2" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="FN2" t="n">
-        <v>8513839</v>
-      </c>
-      <c r="FO2" t="n">
-        <v>110.943085</v>
-      </c>
-      <c r="FP2" t="inlineStr">
+      <c r="FT2" t="inlineStr">
         <is>
           <t>JPMorgan Chase &amp;</t>
         </is>
       </c>
-      <c r="FQ2" t="n">
-        <v>3.8648</v>
+      <c r="FU2" t="n">
+        <v>3.9058</v>
       </c>
     </row>
   </sheetData>
